--- a/src/test/resources/Incident.xlsx
+++ b/src/test/resources/Incident.xlsx
@@ -3,14 +3,9 @@
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
   <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29029"/>
   <workbookPr defaultThemeVersion="166925"/>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Sandesh Velhal\eclipse-workspace\Servicenow-AllModule\src\test\resources\"/>
-    </mc:Choice>
-  </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9114DB09-EB68-4928-963F-1D80ED564B93}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:801_{0BEF9261-37D3-456B-96D3-A03D3A58E127}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-109" yWindow="-109" windowWidth="26301" windowHeight="14169" activeTab="2" xr2:uid="{47AEF9C5-A68B-4616-944B-F17818BC6EA4}"/>
+    <workbookView xWindow="-109" yWindow="-109" windowWidth="26301" windowHeight="14169" xr2:uid="{47AEF9C5-A68B-4616-944B-F17818BC6EA4}"/>
   </bookViews>
   <sheets>
     <sheet name="Create_Inc" sheetId="1" r:id="rId1"/>
@@ -19,6 +14,7 @@
     <sheet name="Normal_Change" sheetId="4" r:id="rId4"/>
   </sheets>
   <calcPr calcId="0"/>
+  <oleSize ref="A1:O7"/>
   <extLst>
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
       <x15:workbookPr chartTrackingRefBase="1"/>
@@ -853,6 +849,21 @@
 </file>
 
 <file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
+<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
+  <documentManagement/>
+</p:properties>
+</file>
+
+<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
+<?mso-contentType ?>
+<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
+  <Display>DocumentLibraryForm</Display>
+  <Edit>DocumentLibraryForm</Edit>
+  <New>DocumentLibraryForm</New>
+</FormTemplates>
+</file>
+
+<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
 <ct:contentTypeSchema xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" ct:_="" ma:_="" ma:contentTypeName="Document" ma:contentTypeID="0x01010073343488A879F648A8233DD2750A8BE0" ma:contentTypeVersion="4" ma:contentTypeDescription="Create a new document." ma:contentTypeScope="" ma:versionID="aecf8f046f0335461bceda7cb2834bf5">
   <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:ns3="2e67f5e3-5d1b-4bca-95ff-bb1bae13fe95" targetNamespace="http://schemas.microsoft.com/office/2006/metadata/properties" ma:root="true" ma:fieldsID="7183a3b8e113dde5e82283a519c12d21" ns3:_="">
     <xsd:import namespace="2e67f5e3-5d1b-4bca-95ff-bb1bae13fe95"/>
@@ -996,22 +1007,31 @@
 </ct:contentTypeSchema>
 </file>
 
-<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
-<?mso-contentType ?>
-<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
-  <Display>DocumentLibraryForm</Display>
-  <Edit>DocumentLibraryForm</Edit>
-  <New>DocumentLibraryForm</New>
-</FormTemplates>
-</file>
-
-<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
-<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
-  <documentManagement/>
-</p:properties>
-</file>
-
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{7AAD2946-464E-4E64-9A2E-8B630789DBB2}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://www.w3.org/XML/1998/namespace"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
+    <ds:schemaRef ds:uri="2e67f5e3-5d1b-4bca-95ff-bb1bae13fe95"/>
+    <ds:schemaRef ds:uri="http://purl.org/dc/terms/"/>
+    <ds:schemaRef ds:uri="http://schemas.openxmlformats.org/package/2006/metadata/core-properties"/>
+    <ds:schemaRef ds:uri="http://purl.org/dc/dcmitype/"/>
+    <ds:schemaRef ds:uri="http://purl.org/dc/elements/1.1/"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
+</file>
+
+<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{CAA51041-64D4-4374-9F9B-AFEDFCEF6388}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
+</file>
+
+<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{C9D8316B-DDF9-4C31-BB62-1D72B0CB79F9}">
   <ds:schemaRefs>
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/contentType"/>
@@ -1029,30 +1049,6 @@
 </ds:datastoreItem>
 </file>
 
-<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{CAA51041-64D4-4374-9F9B-AFEDFCEF6388}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
-</file>
-
-<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{7AAD2946-464E-4E64-9A2E-8B630789DBB2}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://www.w3.org/XML/1998/namespace"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
-    <ds:schemaRef ds:uri="2e67f5e3-5d1b-4bca-95ff-bb1bae13fe95"/>
-    <ds:schemaRef ds:uri="http://purl.org/dc/terms/"/>
-    <ds:schemaRef ds:uri="http://schemas.openxmlformats.org/package/2006/metadata/core-properties"/>
-    <ds:schemaRef ds:uri="http://purl.org/dc/dcmitype/"/>
-    <ds:schemaRef ds:uri="http://purl.org/dc/elements/1.1/"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
-</file>
-
 <file path=docMetadata/LabelInfo.xml><?xml version="1.0" encoding="utf-8"?>
 <clbl:labelList xmlns:clbl="http://schemas.microsoft.com/office/2020/mipLabelMetadata">
   <clbl:label id="{d4def53c-905d-442a-ba22-72ae0f5bcf4f}" enabled="1" method="Standard" siteId="{6c637512-c417-4e78-9d62-b61258e4b619}" removed="0"/>
